--- a/BWI/bestwine_output/bestwine_Vietnam.xlsx
+++ b/BWI/bestwine_output/bestwine_Vietnam.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA203"/>
+  <dimension ref="A1:AA204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19327,6 +19327,83 @@
       <c r="Z203" s="2" t="inlineStr"/>
       <c r="AA203" s="2" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>SÀNH VANG</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>SÀNH VANG</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>59220</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh, Quận 7</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>34 Đường C</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://sanhvang.com</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>sanhvangsg@gmail.com</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="R204" s="2" t="inlineStr"/>
+      <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr"/>
+      <c r="X204" s="2" t="inlineStr"/>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Vietnam.xlsx
+++ b/BWI/bestwine_output/bestwine_Vietnam.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA204"/>
+  <dimension ref="A1:AA214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19404,6 +19404,912 @@
       <c r="Z204" s="2" t="inlineStr"/>
       <c r="AA204" s="2" t="inlineStr"/>
     </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>KSP GLOBAL IMPORT EXPORT COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr"/>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>167787</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>116 Nguyễn Văn Quỳ</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://kspglobalwines.com</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>71440</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>orders@kspglobalwines.com</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr"/>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>317136151</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr"/>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kspglobalwines</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@KSPWINES/</t>
+        </is>
+      </c>
+      <c r="W205" s="2" t="inlineStr">
+        <is>
+          <t>Nguyen Trung Khanh Phu</t>
+        </is>
+      </c>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA LUU KIM IMPORT EXPORT COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ITALIA LUU KIM IMPORT EXPORT </t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>167786</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Ha Noi</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>1 Huynh Tan Phat Street,</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>http://italialuukim.com</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>224717</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>haunt@italialuukim.com</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>+84 24 3724 7439</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>312548828</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr"/>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italialuukimvietnam</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Nguyen Trung Hau</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>DANGTAU ENTERTAINMENT COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr"/>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>167780</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Ha Noi</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>31 Nguyen Gia Thieu,</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://dangtauwhisky.com</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>193104</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>dt@dangtauwhisky.co.uk</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr"/>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>110578996</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dangtau-whisky/</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/dangtauwhisky</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dangtauwhisky.official/</t>
+        </is>
+      </c>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@dangtauwhisky</t>
+        </is>
+      </c>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Nguyen Hai Dang</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>124 Dien Bien Phu,</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glouglouwineshop.com</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>glouglou@vinobeer.fr</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr"/>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>317884615</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/glouglou-wines-vietnam/</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glouglouwinesvietnam</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glouglouwines/</t>
+        </is>
+      </c>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>Cedric Bey</t>
+        </is>
+      </c>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> General Manager </t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cedric-bey-6b616690/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>124 Dien Bien Phu,</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glouglouwineshop.com</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>glouglou@vinobeer.fr</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr"/>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>317884615</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/glouglou-wines-vietnam/</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glouglouwinesvietnam</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glouglouwines/</t>
+        </is>
+      </c>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Axel Riffaud</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/axel-riffaud-89201a51/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>GLOUGLOU WINES</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>124 Dien Bien Phu,</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glouglouwineshop.com</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>glouglou@vinobeer.fr</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>317884615</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/glouglou-wines-vietnam/</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glouglouwinesvietnam</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glouglouwines/</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Lyna Trần</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/lyna-tr%e1%ba%a7n-2635b1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>WINE COLOR LIMITED LIABILITY COMPANY</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>WINE COLOR</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>167774</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>20 Street No 2,</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://winecolor.vn</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>99093</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>info.winecolor@gmail.com</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr"/>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>317973985</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr"/>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/WINE-COLOR/100093289496874/</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr">
+        <is>
+          <t>Lam Thi Hong Diem</t>
+        </is>
+      </c>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>TGV FINE WINES VIET NAM JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>167773</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Ha Noi</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>33-35 Van Phuc Street</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finewinesvn.com</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>contact@finewinesvn.com</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>+84 28 3824 1705</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>108467939</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr"/>
+      <c r="S212" s="2" t="inlineStr"/>
+      <c r="T212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr">
+        <is>
+          <t>Hoang Thi Thu Giang</t>
+        </is>
+      </c>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>TRUONG GIA SAI GON JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>TRUONG GIA SAI GON</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>167772</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Thu Duc</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>280C25 Luong Dinh Cua Street</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://truonggiasaigon.vn</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>104084</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>info@truonggiasaigon.com</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>+84 28 3620 1386</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>315453211</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr"/>
+      <c r="S213" s="2" t="inlineStr"/>
+      <c r="T213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr"/>
+      <c r="X213" s="2" t="inlineStr"/>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>WINE CENTER VIET NAM COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>WINE CENTER VIET NAM</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>167770</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>1162/2/9 Truong Sa,</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://winecenter.vn</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>winecentervn@gmail.com</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>315274741</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr"/>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ruouvangwinecenter</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>Do Tri Duc</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Vietnam.xlsx
+++ b/BWI/bestwine_output/bestwine_Vietnam.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA214"/>
+  <dimension ref="A1:AA221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20310,6 +20310,617 @@
       <c r="Z214" s="2" t="inlineStr"/>
       <c r="AA214" s="2" t="inlineStr"/>
     </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>K-WINE COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>K-WINE CO., LTD</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>167862</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>15A/57C Le Thanh Ton Street,</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://soulwinevietnam.vn</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>51834</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>ctcpsoulwine@gmail.com</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>315240284</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr"/>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/soulwine.vn</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>Truong Thi Kim Anh</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>TM WINE HA NOI JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>TM WINE HA NOI</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>167861</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Ha Noi</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Bt25, Handico 7, 68A, Vo Chi Cong Street</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://tmwine.vn</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>20300</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>cskh@tmwine.vn</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr"/>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>110322722</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tm-wine-viet-nam/</t>
+        </is>
+      </c>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tmwine.vn/</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>Mai Van Duyen</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>LAI VINH COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>LAIVINH</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>167860</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>A3.8, Everich 3 Residential Area, Phu Thuan Street</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>https://laivinh.com.vn</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>13993</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>kt@laivinh.com</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>316078210</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr"/>
+      <c r="S217" s="2" t="inlineStr"/>
+      <c r="T217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr">
+        <is>
+          <t>Tran Duc Tinh</t>
+        </is>
+      </c>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>Chairman</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>LAI VINH COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>LAIVINH</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>167860</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>A3.8, Everich 3 Residential Area, Phu Thuan Street</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://laivinh.com.vn</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>13993</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>kt@laivinh.com</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>316078210</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr"/>
+      <c r="S218" s="2" t="inlineStr"/>
+      <c r="T218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr">
+        <is>
+          <t>Doan Linh Phong</t>
+        </is>
+      </c>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>NATIVE WINES JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>NATIVE WINES., JSC</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>167859</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Ha Noi</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>C20, Lane 109, Truong Chinh Street,</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>https://nativewines.vn</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>12731</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>nativewines9086@gmail.com</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr"/>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>110417501</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr"/>
+      <c r="S219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/NativeWines9086/</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr"/>
+      <c r="W219" s="2" t="inlineStr"/>
+      <c r="X219" s="2" t="inlineStr"/>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>SAY SAY WINE COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>SAY SAY WINE CO., LTD</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>167857</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Thu Duc</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>428 Lien Phuong</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://saysaywine.com</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>198186</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>anhvy@saysaywine.com</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>317091655</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr"/>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/saysaywine/</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr">
+        <is>
+          <t>Nguyen Vuong Anh Vy</t>
+        </is>
+      </c>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>NHAT VANG TM JOINT STOCK COMPANY</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>NHAT VANG TM JSC</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>167840</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Hai Duong</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Hai Duong</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>381 Truong Chinh,</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://nhatvang.com</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>12794</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>nhatvang2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>801338256</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr"/>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Nhatvangwinelounge</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr">
+        <is>
+          <t>Nguyen Dang Tam</t>
+        </is>
+      </c>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>Chairman</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Vietnam.xlsx
+++ b/BWI/bestwine_output/bestwine_Vietnam.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA221"/>
+  <dimension ref="A1:AA222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20921,6 +20921,87 @@
       <c r="Z221" s="2" t="inlineStr"/>
       <c r="AA221" s="2" t="inlineStr"/>
     </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>SSP Joint Stock Company</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>SSP Joint Stock Company</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>25408</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội, Hoàng Mai</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Ngách 147A/60, đường đôi</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>116916</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>http://sspgroup.vn</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>info@sspgroup.vn</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr"/>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>0104172726</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr"/>
+      <c r="S222" s="2" t="inlineStr"/>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr"/>
+      <c r="X222" s="2" t="inlineStr"/>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Vietnam.xlsx
+++ b/BWI/bestwine_output/bestwine_Vietnam.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21002,6 +21002,91 @@
       <c r="Z222" s="2" t="inlineStr"/>
       <c r="AA222" s="2" t="inlineStr"/>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Shop Tuan Anh</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Shop Tuan Anh</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>108659</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Tân Bình</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>696 Lạc Long Quân</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://chuyenruoungoai.com</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>chuyenruoungoai247@gmail.com</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr"/>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr"/>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chuyenruoungoai-wine-spirits/</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ruoungoaigiasihcm</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>Trung Hieu</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>Retail Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/trung-hieu-quach-ngoc-655866176/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
